--- a/hosp3up.xlsx
+++ b/hosp3up.xlsx
@@ -407,17 +407,17 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>contact</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>phone</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>zip</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -476,14 +476,14 @@
           <t>NY</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>12308</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>518-243-4051</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>12308</t>
         </is>
       </c>
       <c r="N2">
@@ -575,14 +575,14 @@
           <t>GA</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>30046</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>678-312-4516</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>30046</t>
         </is>
       </c>
       <c r="N4">
@@ -637,14 +637,14 @@
           <t>GA</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>30014</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>770-385-4439</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>30014</t>
         </is>
       </c>
       <c r="N5">
@@ -701,17 +701,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>04401</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>BLOOD BANK</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>207-973-7646</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>04401</t>
         </is>
       </c>
       <c r="N6">
@@ -766,14 +766,14 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>91355</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>661-253-8000 x8508</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>91355</t>
         </is>
       </c>
       <c r="N7">
@@ -828,14 +828,14 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>90301</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>213-502-1900</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>90301</t>
         </is>
       </c>
       <c r="N8">
@@ -892,17 +892,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>54702</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>BLOOD BANK</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>715-838-3203</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>54702</t>
         </is>
       </c>
       <c r="N9">
@@ -957,14 +957,14 @@
           <t>UT</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>84157</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>801-507-5092</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>84157</t>
         </is>
       </c>
       <c r="N10">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t>29526</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>JOHN ORR</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>843-347-8280</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>29526</t>
         </is>
       </c>
       <c r="N11">
@@ -1086,14 +1086,14 @@
           <t>IN</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>46202</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>317-274-7637</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>46202</t>
         </is>
       </c>
       <c r="N12">
@@ -1150,17 +1150,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t>60153</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>BLOOD BANK</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>708-216-3951</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>60153</t>
         </is>
       </c>
       <c r="N13">
@@ -1215,14 +1215,14 @@
           <t>TX</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>75246</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>214-820-3263</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>75246</t>
         </is>
       </c>
       <c r="N14">
@@ -1279,17 +1279,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t>00959</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t>BLOOD BANK</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>787-620-8181</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>00959</t>
         </is>
       </c>
       <c r="N15">
@@ -1346,17 +1346,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t>95051</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t>SHARON BRADBURN</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>408-851-6310</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>95051</t>
         </is>
       </c>
       <c r="N16">
@@ -1411,14 +1411,14 @@
           <t>MA</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>01040</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t>413-536-5221 x5531</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>01040</t>
         </is>
       </c>
       <c r="N17">
@@ -1473,14 +1473,14 @@
           <t>MO</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>63131</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>314-996-4263</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>63131</t>
         </is>
       </c>
       <c r="N18">
@@ -1537,17 +1537,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t>97838-9696</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t>BLOOD BANK</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>541-667-3575</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>97838-9696</t>
         </is>
       </c>
       <c r="N19">
@@ -1604,17 +1604,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t>08015</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t>BLOOD BANK</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>609-893-6611</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>08015</t>
         </is>
       </c>
       <c r="N20">
@@ -1669,14 +1669,14 @@
           <t>OH</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>43952</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t>614-264-8000</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>43952</t>
         </is>
       </c>
       <c r="N21">
@@ -1733,17 +1733,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t>29801-2792</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t>TOM LOCKETT</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>803-641-5168</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>29801-2792</t>
         </is>
       </c>
       <c r="N22">
@@ -1800,17 +1800,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t>29505</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t>MOLLY BUSH</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>843-674-2570</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>29505</t>
         </is>
       </c>
       <c r="N23">
@@ -1865,14 +1865,14 @@
           <t>SC</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>29204</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t>803-256-5789</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>29204</t>
         </is>
       </c>
       <c r="N24">
@@ -1929,17 +1929,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t>03246</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t>SCOTT GAGE</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>603-527-7022</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>03246</t>
         </is>
       </c>
       <c r="N25">
@@ -1994,14 +1994,14 @@
           <t>UT</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>84094</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t>801-576-2600</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>84094</t>
         </is>
       </c>
       <c r="N26">
@@ -2058,17 +2058,17 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t>84060</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t>KELLY CRAM</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>435-658-7030</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>84060</t>
         </is>
       </c>
       <c r="N27">
@@ -2123,14 +2123,14 @@
           <t>UT</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>84065</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t>801-285-2240</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>84065</t>
         </is>
       </c>
       <c r="N28">
@@ -2187,17 +2187,17 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t>46037</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t>GAIL FITZGERALD</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>317 678-1436</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>46037</t>
         </is>
       </c>
       <c r="N29">

--- a/hosp3up.xlsx
+++ b/hosp3up.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1101 NOTT ST</t>
+          <t>1101 NOTT STREET</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -479,11 +479,6 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>12308</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>518-243-4051</t>
         </is>
       </c>
       <c r="N2">
@@ -523,6 +518,31 @@
       <c r="G3">
         <v>37.2675978170382</v>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>329 COLUMBIA ST</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>UTICA</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>13502</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>HARRY HENZE</t>
+        </is>
+      </c>
       <c r="N3">
         <v>43.11016</v>
       </c>
@@ -580,11 +600,6 @@
           <t>30046</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>678-312-4516</t>
-        </is>
-      </c>
       <c r="N4">
         <v>33.964343</v>
       </c>
@@ -686,12 +701,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>489 STATE STREET</t>
+          <t>43 WHITING HILL ROAD</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BANGOR</t>
+          <t>BREWER</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -701,17 +716,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>04401</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>BLOOD BANK</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>207-973-7646</t>
+          <t>04412</t>
         </is>
       </c>
       <c r="N6">
@@ -753,7 +758,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>23845 WEST MC BEAN PARKWAY</t>
+          <t>PO BOX 55279</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -769,11 +774,6 @@
       <c r="K7" t="inlineStr">
         <is>
           <t>91355</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>661-253-8000 x8508</t>
         </is>
       </c>
       <c r="N7">
@@ -815,7 +815,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>555 EAST HARDY STREET</t>
+          <t>PO BOX 6095</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -830,12 +830,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>90301</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>213-502-1900</t>
+          <t>90307</t>
         </is>
       </c>
       <c r="N8">
@@ -944,7 +939,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5121 SOUTH COTTONWOOD STREET</t>
+          <t>5121 SOUTH COTTONWOOD</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -959,12 +954,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>84157</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>801-507-5092</t>
+          <t>84123</t>
         </is>
       </c>
       <c r="N10">
@@ -1073,7 +1063,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1701 N SENATE BLVD</t>
+          <t>C/O IU HLTH RILEY HOSP FOR CHN</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1089,11 +1079,6 @@
       <c r="K12" t="inlineStr">
         <is>
           <t>46202</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>317-274-7637</t>
         </is>
       </c>
       <c r="N12">
@@ -1153,16 +1138,6 @@
           <t>60153</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>BLOOD BANK</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>708-216-3951</t>
-        </is>
-      </c>
       <c r="N13">
         <v>41.85992</v>
       </c>
@@ -1202,7 +1177,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3500 GASTON AVENUE</t>
+          <t>3500 GASTON</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1218,11 +1193,6 @@
       <c r="K14" t="inlineStr">
         <is>
           <t>75246</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>214-820-3263</t>
         </is>
       </c>
       <c r="N14">
@@ -1478,11 +1448,6 @@
           <t>63131</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>314-996-4263</t>
-        </is>
-      </c>
       <c r="N18">
         <v>38.635477</v>
       </c>
@@ -1537,17 +1502,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>97838-9696</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>BLOOD BANK</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>541-667-3575</t>
+          <t>97838</t>
         </is>
       </c>
       <c r="N19">
@@ -1607,16 +1562,6 @@
           <t>08015</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>BLOOD BANK</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>609-893-6611</t>
-        </is>
-      </c>
       <c r="N20">
         <v>39.977588</v>
       </c>
@@ -1718,7 +1663,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>302 UNIVERSITY PKWY</t>
+          <t>PO BOX 1117</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1733,17 +1678,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>29801-2792</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>TOM LOCKETT</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>803-641-5168</t>
+          <t>29801</t>
         </is>
       </c>
       <c r="N22">
@@ -1803,16 +1738,6 @@
           <t>29505</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>MOLLY BUSH</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>843-674-2570</t>
-        </is>
-      </c>
       <c r="N23">
         <v>34.158794</v>
       </c>
@@ -1914,7 +1839,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>80 HIGHLAND ST</t>
+          <t>HIGHLAND STREET</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1930,16 +1855,6 @@
       <c r="K25" t="inlineStr">
         <is>
           <t>03246</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>SCOTT GAGE</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>603-527-7022</t>
         </is>
       </c>
       <c r="N25">
@@ -1981,12 +1896,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>9660 SOUTH 1300 EAST</t>
+          <t>INTERMOUNTAIN HEALTHCARE</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SANDY</t>
+          <t>SALT LAKE CITY</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1996,12 +1911,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>84094</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>801-576-2600</t>
+          <t>84111</t>
         </is>
       </c>
       <c r="N26">
@@ -2061,16 +1971,6 @@
           <t>84060</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>KELLY CRAM</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>435-658-7030</t>
-        </is>
-      </c>
       <c r="N27">
         <v>40.687572</v>
       </c>
@@ -2126,11 +2026,6 @@
       <c r="K28" t="inlineStr">
         <is>
           <t>84065</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>801-285-2240</t>
         </is>
       </c>
       <c r="N28">

--- a/hosp3up.xlsx
+++ b/hosp3up.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1101 NOTT STREET</t>
+          <t>1101 NOTT ST</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -479,6 +479,11 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>12308</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>518-243-4051</t>
         </is>
       </c>
       <c r="N2">
@@ -518,31 +523,6 @@
       <c r="G3">
         <v>37.2675978170382</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>329 COLUMBIA ST</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>UTICA</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>NY</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>13502</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>HARRY HENZE</t>
-        </is>
-      </c>
       <c r="N3">
         <v>43.11016</v>
       </c>
@@ -600,6 +580,11 @@
           <t>30046</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>678-312-4516</t>
+        </is>
+      </c>
       <c r="N4">
         <v>33.964343</v>
       </c>
@@ -701,12 +686,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>43 WHITING HILL ROAD</t>
+          <t>489 STATE STREET</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BREWER</t>
+          <t>BANGOR</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -716,7 +701,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>04412</t>
+          <t>04401</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>BLOOD BANK</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>207-973-7646</t>
         </is>
       </c>
       <c r="N6">
@@ -758,7 +753,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>PO BOX 55279</t>
+          <t>23845 WEST MC BEAN PARKWAY</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -774,6 +769,11 @@
       <c r="K7" t="inlineStr">
         <is>
           <t>91355</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>661-253-8000 x8508</t>
         </is>
       </c>
       <c r="N7">
@@ -815,7 +815,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>PO BOX 6095</t>
+          <t>555 EAST HARDY STREET</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -830,7 +830,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>90307</t>
+          <t>90301</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>213-502-1900</t>
         </is>
       </c>
       <c r="N8">
@@ -939,7 +944,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5121 SOUTH COTTONWOOD</t>
+          <t>5121 SOUTH COTTONWOOD STREET</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -954,7 +959,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>84123</t>
+          <t>84157</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>801-507-5092</t>
         </is>
       </c>
       <c r="N10">
@@ -1063,7 +1073,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>C/O IU HLTH RILEY HOSP FOR CHN</t>
+          <t>1701 N SENATE BLVD</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1079,6 +1089,11 @@
       <c r="K12" t="inlineStr">
         <is>
           <t>46202</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>317-274-7637</t>
         </is>
       </c>
       <c r="N12">
@@ -1138,6 +1153,16 @@
           <t>60153</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>BLOOD BANK</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>708-216-3951</t>
+        </is>
+      </c>
       <c r="N13">
         <v>41.85992</v>
       </c>
@@ -1177,7 +1202,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3500 GASTON</t>
+          <t>3500 GASTON AVENUE</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1193,6 +1218,11 @@
       <c r="K14" t="inlineStr">
         <is>
           <t>75246</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>214-820-3263</t>
         </is>
       </c>
       <c r="N14">
@@ -1448,6 +1478,11 @@
           <t>63131</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>314-996-4263</t>
+        </is>
+      </c>
       <c r="N18">
         <v>38.635477</v>
       </c>
@@ -1502,7 +1537,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>97838</t>
+          <t>97838-9696</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>BLOOD BANK</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>541-667-3575</t>
         </is>
       </c>
       <c r="N19">
@@ -1562,6 +1607,16 @@
           <t>08015</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>BLOOD BANK</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>609-893-6611</t>
+        </is>
+      </c>
       <c r="N20">
         <v>39.977588</v>
       </c>
@@ -1663,7 +1718,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>PO BOX 1117</t>
+          <t>302 UNIVERSITY PKWY</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1678,7 +1733,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>29801</t>
+          <t>29801-2792</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>TOM LOCKETT</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>803-641-5168</t>
         </is>
       </c>
       <c r="N22">
@@ -1738,6 +1803,16 @@
           <t>29505</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>MOLLY BUSH</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>843-674-2570</t>
+        </is>
+      </c>
       <c r="N23">
         <v>34.158794</v>
       </c>
@@ -1839,7 +1914,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>HIGHLAND STREET</t>
+          <t>80 HIGHLAND ST</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1855,6 +1930,16 @@
       <c r="K25" t="inlineStr">
         <is>
           <t>03246</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>SCOTT GAGE</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>603-527-7022</t>
         </is>
       </c>
       <c r="N25">
@@ -1896,12 +1981,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>INTERMOUNTAIN HEALTHCARE</t>
+          <t>9660 SOUTH 1300 EAST</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SALT LAKE CITY</t>
+          <t>SANDY</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1911,7 +1996,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>84111</t>
+          <t>84094</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>801-576-2600</t>
         </is>
       </c>
       <c r="N26">
@@ -1971,6 +2061,16 @@
           <t>84060</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>KELLY CRAM</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>435-658-7030</t>
+        </is>
+      </c>
       <c r="N27">
         <v>40.687572</v>
       </c>
@@ -2026,6 +2126,11 @@
       <c r="K28" t="inlineStr">
         <is>
           <t>84065</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>801-285-2240</t>
         </is>
       </c>
       <c r="N28">

--- a/hosp3up.xlsx
+++ b/hosp3up.xlsx
@@ -523,6 +523,31 @@
       <c r="G3">
         <v>37.2675978170382</v>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>329 COLUMBIA ST</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>UTICA</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>13502</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>HARRY HENZE</t>
+        </is>
+      </c>
       <c r="N3">
         <v>43.11016</v>
       </c>
